--- a/実装ノート.xlsx
+++ b/実装ノート.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F35F7EE-43ED-45D6-B26D-512C0E6ABB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3C20EF-951D-471F-B63D-D90A85874E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -494,17 +494,27 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>HP画像をHPの被ダメージ時にじわじわ減少</t>
+    <rPh sb="2" eb="4">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t xml:space="preserve">・ 敵に吹っ飛ばされた時の再スポーンの吹っ飛ばしを無効化
 ・ 再スポーン時にジャンプを無効化
 ・ 遠距離敵の攻撃タイミングを調整
-・ プレイヤーが床に埋もれていても、移動する敵を待機状態にする
-・ プレイヤーが床に埋もれていても、遠距離の弾がプレイヤーに攻撃する
-・ステージのブロック生成の読み取り順を"前→奥"から"奥→前"に変更
+・ プレイヤーが床下にいるとき、デーモンはアニメーションを待機状態にする
+・ プレイヤーが床下にいるとき、遠距離の弾がプレイヤーに攻撃する
+・ステージのブロック生成の生成する順番を"前→奥"から"奥→前"に変更
 　↳ これにより、データどうりの見た目で生成されるようになる
-・ステージデータに生成最大数を超えたデータを入力したときの例外スローを対策
+・ステージデータに「生成最大数を超えたデータを入力」したときに、最大数以上のデータは読み込まないようにする
 　↳ 例:) 生成最大数30×30でセル番号(BA,40)に生成しても正常に動作する
 ・ステージデータの読み込む領域で「未入力」か「データ数値外」か「文字列が含まれる」のとき、
-　"空モデル"を描画して例外スローを対策
+　"空のモデル"を描画して例外スローを対策
 ・ </t>
     <rPh sb="2" eb="3">
       <t>テキ</t>
@@ -545,145 +555,141 @@
     <rPh sb="73" eb="74">
       <t>ユカ</t>
     </rPh>
-    <rPh sb="75" eb="76">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="87" eb="88">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="115" eb="118">
+    <rPh sb="74" eb="75">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="118" eb="121">
       <t>エンキョリ</t>
     </rPh>
-    <rPh sb="119" eb="120">
+    <rPh sb="122" eb="123">
       <t>タマ</t>
     </rPh>
-    <rPh sb="127" eb="129">
+    <rPh sb="130" eb="132">
       <t>コウゲキ</t>
     </rPh>
-    <rPh sb="146" eb="147">
+    <rPh sb="157" eb="158">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="159" eb="160">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="164" eb="165">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="166" eb="167">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="185" eb="186">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="187" eb="188">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="189" eb="191">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="209" eb="211">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="216" eb="217">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="223" eb="225">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="231" eb="233">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="235" eb="238">
+      <t>サイダイスウ</t>
+    </rPh>
+    <rPh sb="238" eb="240">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="245" eb="246">
       <t>ヨ</t>
     </rPh>
-    <rPh sb="148" eb="149">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="150" eb="151">
-      <t>ジュン</t>
-    </rPh>
-    <rPh sb="153" eb="154">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="155" eb="156">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="160" eb="161">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="162" eb="163">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="184" eb="185">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="186" eb="187">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="188" eb="190">
+    <rPh sb="247" eb="248">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="257" eb="258">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="261" eb="265">
+      <t>セイセイサイダイ</t>
+    </rPh>
+    <rPh sb="265" eb="266">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="274" eb="276">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="284" eb="286">
       <t>セイセイ</t>
     </rPh>
-    <rPh sb="208" eb="210">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="210" eb="213">
-      <t>サイダイスウ</t>
-    </rPh>
-    <rPh sb="214" eb="215">
+    <rPh sb="289" eb="291">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="292" eb="294">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="306" eb="307">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="308" eb="309">
       <t>コ</t>
     </rPh>
-    <rPh sb="221" eb="223">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="228" eb="230">
+    <rPh sb="310" eb="312">
+      <t>リョウイキ</t>
+    </rPh>
+    <rPh sb="314" eb="317">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="323" eb="325">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="325" eb="326">
+      <t>ガイ</t>
+    </rPh>
+    <rPh sb="329" eb="332">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="333" eb="334">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="345" eb="346">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="348" eb="349">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="352" eb="354">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="356" eb="358">
       <t>レイガイ</t>
     </rPh>
-    <rPh sb="234" eb="236">
-      <t>タイサク</t>
-    </rPh>
-    <rPh sb="240" eb="241">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="244" eb="248">
-      <t>セイセイサイダイ</t>
-    </rPh>
-    <rPh sb="248" eb="249">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="257" eb="259">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="267" eb="269">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="272" eb="274">
-      <t>セイジョウ</t>
-    </rPh>
-    <rPh sb="275" eb="277">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="289" eb="290">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="291" eb="292">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="293" eb="295">
-      <t>リョウイキ</t>
-    </rPh>
-    <rPh sb="297" eb="300">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="306" eb="308">
-      <t>スウチ</t>
-    </rPh>
-    <rPh sb="308" eb="309">
-      <t>ガイ</t>
-    </rPh>
-    <rPh sb="312" eb="315">
-      <t>モジレツ</t>
-    </rPh>
-    <rPh sb="316" eb="317">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="328" eb="329">
-      <t>カラ</t>
-    </rPh>
-    <rPh sb="334" eb="336">
-      <t>ビョウガ</t>
-    </rPh>
-    <rPh sb="338" eb="340">
-      <t>レイガイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HP画像をHPの被ダメージ時にじわじわ減少</t>
-    <rPh sb="2" eb="4">
-      <t>ガゾウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ゲンショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップデータの書き込み時の例外スロー対策</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップデータの書き込み時の例外スロー対策(詳細は特質事項に記入)</t>
     <rPh sb="7" eb="9">
       <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>トクシツジコウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キニュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -692,7 +698,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -716,6 +722,14 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐ明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐ明朝"/>
@@ -819,7 +833,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -835,14 +849,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -856,16 +876,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1168,36 +1185,36 @@
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11">
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13">
         <v>2416026</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="O6" s="10" t="s">
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="O6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="11" t="s">
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="11"/>
-      <c r="Z6" s="11"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C7" s="3"/>
@@ -1235,39 +1252,39 @@
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
       <c r="R10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S10" s="13" t="s">
+      <c r="S10" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
     </row>
     <row r="11" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C11" s="5" t="s">
@@ -1276,39 +1293,39 @@
       <c r="D11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
       <c r="R11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S11" s="7" t="s">
+      <c r="S11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
-      <c r="AE11" s="7"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="10"/>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C12" s="5" t="s">
@@ -1317,39 +1334,39 @@
       <c r="D12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
       <c r="R12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
-      <c r="AE12" s="7"/>
+      <c r="S12" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C13" s="5" t="s">
@@ -1358,39 +1375,39 @@
       <c r="D13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
       <c r="R13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S13" s="7" t="s">
+      <c r="S13" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
-      <c r="AE13" s="7"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="10"/>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C14" s="5" t="s">
@@ -1399,39 +1416,39 @@
       <c r="D14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
       <c r="R14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S14" s="7" t="s">
+      <c r="S14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
-      <c r="AE14" s="7"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C15" s="5" t="s">
@@ -1440,35 +1457,35 @@
       <c r="D15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
       <c r="R15" s="6"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="16"/>
-      <c r="AE15" s="17"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="8"/>
+      <c r="AD15" s="8"/>
+      <c r="AE15" s="9"/>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C16" s="5" t="s">
@@ -1477,35 +1494,35 @@
       <c r="D16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
       <c r="R16" s="6"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
-      <c r="AE16" s="7"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
     </row>
     <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="5" t="s">
@@ -1514,35 +1531,35 @@
       <c r="D17" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="17"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="9"/>
       <c r="R17" s="6"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
-      <c r="AE17" s="7"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
     </row>
     <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="5" t="s">
@@ -1551,70 +1568,72 @@
       <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="17"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="9"/>
       <c r="R18" s="6"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7"/>
-      <c r="AE18" s="7"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
     </row>
     <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="15" t="s">
+      <c r="D19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="17"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="9"/>
       <c r="R19" s="6"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7"/>
-      <c r="AE19" s="7"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+      <c r="AD19" s="10"/>
+      <c r="AE19" s="10"/>
     </row>
     <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="5" t="s">
@@ -1623,74 +1642,76 @@
       <c r="D20" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
       <c r="R20" s="6"/>
-      <c r="S20" s="7" t="s">
+      <c r="S20" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
-      <c r="AE20" s="7"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="18"/>
+      <c r="Y20" s="18"/>
+      <c r="Z20" s="18"/>
+      <c r="AA20" s="18"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="18"/>
+      <c r="AE20" s="18"/>
     </row>
     <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7" t="s">
+      <c r="D21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
       <c r="R21" s="6"/>
-      <c r="S21" s="7" t="s">
+      <c r="S21" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="7"/>
-      <c r="AE21" s="7"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="18"/>
+      <c r="AB21" s="18"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="18"/>
+      <c r="AE21" s="18"/>
     </row>
     <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="5" t="s">
@@ -1699,148 +1720,154 @@
       <c r="D22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
       <c r="R22" s="6"/>
-      <c r="S22" s="7" t="s">
+      <c r="S22" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="7"/>
-      <c r="AC22" s="7"/>
-      <c r="AD22" s="7"/>
-      <c r="AE22" s="7"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Y22" s="18"/>
+      <c r="Z22" s="18"/>
+      <c r="AA22" s="18"/>
+      <c r="AB22" s="18"/>
+      <c r="AC22" s="18"/>
+      <c r="AD22" s="18"/>
+      <c r="AE22" s="18"/>
     </row>
     <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7" t="s">
+      <c r="D23" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
       <c r="R23" s="6"/>
-      <c r="S23" s="7" t="s">
+      <c r="S23" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="7"/>
-      <c r="AC23" s="7"/>
-      <c r="AD23" s="7"/>
-      <c r="AE23" s="7"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10"/>
+      <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10"/>
     </row>
     <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7" t="s">
+      <c r="D24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="7" t="s">
+      <c r="S24" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7"/>
-      <c r="AD24" s="7"/>
-      <c r="AE24" s="7"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+      <c r="AA24" s="10"/>
+      <c r="AB24" s="10"/>
+      <c r="AC24" s="10"/>
+      <c r="AD24" s="10"/>
+      <c r="AE24" s="10"/>
     </row>
     <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="7" t="s">
+      <c r="D25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
       <c r="R25" s="6"/>
-      <c r="S25" s="7" t="s">
+      <c r="S25" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
-      <c r="AD25" s="7"/>
-      <c r="AE25" s="7"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
+      <c r="AA25" s="10"/>
+      <c r="AB25" s="10"/>
+      <c r="AC25" s="10"/>
+      <c r="AD25" s="10"/>
+      <c r="AE25" s="10"/>
     </row>
     <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D27" s="3" t="s">
@@ -1880,429 +1907,421 @@
       </c>
     </row>
     <row r="33" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-      <c r="U33" s="12"/>
-      <c r="V33" s="12"/>
-      <c r="W33" s="12"/>
-      <c r="X33" s="12"/>
-      <c r="Y33" s="12"/>
-      <c r="Z33" s="12"/>
-      <c r="AA33" s="12"/>
-      <c r="AB33" s="12"/>
-      <c r="AC33" s="12"/>
-      <c r="AD33" s="12"/>
-      <c r="AE33" s="12"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
     </row>
     <row r="34" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C34" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="9"/>
-      <c r="AE34" s="9"/>
+      <c r="C34" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="17"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="17"/>
+      <c r="Y34" s="17"/>
+      <c r="Z34" s="17"/>
+      <c r="AA34" s="17"/>
+      <c r="AB34" s="17"/>
+      <c r="AC34" s="17"/>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="17"/>
     </row>
     <row r="35" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9"/>
-      <c r="Y35" s="9"/>
-      <c r="Z35" s="9"/>
-      <c r="AA35" s="9"/>
-      <c r="AB35" s="9"/>
-      <c r="AC35" s="9"/>
-      <c r="AD35" s="9"/>
-      <c r="AE35" s="9"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="17"/>
+      <c r="AB35" s="17"/>
+      <c r="AC35" s="17"/>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
     </row>
     <row r="36" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="9"/>
-      <c r="AE36" s="9"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
+      <c r="Z36" s="17"/>
+      <c r="AA36" s="17"/>
+      <c r="AB36" s="17"/>
+      <c r="AC36" s="17"/>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="17"/>
     </row>
     <row r="37" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="9"/>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="9"/>
-      <c r="AA37" s="9"/>
-      <c r="AB37" s="9"/>
-      <c r="AC37" s="9"/>
-      <c r="AD37" s="9"/>
-      <c r="AE37" s="9"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
+      <c r="Z37" s="17"/>
+      <c r="AA37" s="17"/>
+      <c r="AB37" s="17"/>
+      <c r="AC37" s="17"/>
+      <c r="AD37" s="17"/>
+      <c r="AE37" s="17"/>
     </row>
     <row r="38" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9"/>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="9"/>
-      <c r="AA38" s="9"/>
-      <c r="AB38" s="9"/>
-      <c r="AC38" s="9"/>
-      <c r="AD38" s="9"/>
-      <c r="AE38" s="9"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17"/>
+      <c r="AB38" s="17"/>
+      <c r="AC38" s="17"/>
+      <c r="AD38" s="17"/>
+      <c r="AE38" s="17"/>
     </row>
     <row r="39" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="9"/>
-      <c r="AE39" s="9"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="17"/>
+      <c r="AA39" s="17"/>
+      <c r="AB39" s="17"/>
+      <c r="AC39" s="17"/>
+      <c r="AD39" s="17"/>
+      <c r="AE39" s="17"/>
     </row>
     <row r="40" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
-      <c r="X40" s="9"/>
-      <c r="Y40" s="9"/>
-      <c r="Z40" s="9"/>
-      <c r="AA40" s="9"/>
-      <c r="AB40" s="9"/>
-      <c r="AC40" s="9"/>
-      <c r="AD40" s="9"/>
-      <c r="AE40" s="9"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
+      <c r="Z40" s="17"/>
+      <c r="AA40" s="17"/>
+      <c r="AB40" s="17"/>
+      <c r="AC40" s="17"/>
+      <c r="AD40" s="17"/>
+      <c r="AE40" s="17"/>
     </row>
     <row r="41" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
-      <c r="Y41" s="9"/>
-      <c r="Z41" s="9"/>
-      <c r="AA41" s="9"/>
-      <c r="AB41" s="9"/>
-      <c r="AC41" s="9"/>
-      <c r="AD41" s="9"/>
-      <c r="AE41" s="9"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="17"/>
+      <c r="AA41" s="17"/>
+      <c r="AB41" s="17"/>
+      <c r="AC41" s="17"/>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="17"/>
     </row>
     <row r="42" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="R42" s="9"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="9"/>
-      <c r="AE42" s="9"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="17"/>
+      <c r="U42" s="17"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="17"/>
+      <c r="AA42" s="17"/>
+      <c r="AB42" s="17"/>
+      <c r="AC42" s="17"/>
+      <c r="AD42" s="17"/>
+      <c r="AE42" s="17"/>
     </row>
     <row r="43" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="9"/>
-      <c r="AE43" s="9"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="17"/>
+      <c r="AA43" s="17"/>
+      <c r="AB43" s="17"/>
+      <c r="AC43" s="17"/>
+      <c r="AD43" s="17"/>
+      <c r="AE43" s="17"/>
     </row>
     <row r="44" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9"/>
-      <c r="R44" s="9"/>
-      <c r="S44" s="9"/>
-      <c r="T44" s="9"/>
-      <c r="U44" s="9"/>
-      <c r="V44" s="9"/>
-      <c r="W44" s="9"/>
-      <c r="X44" s="9"/>
-      <c r="Y44" s="9"/>
-      <c r="Z44" s="9"/>
-      <c r="AA44" s="9"/>
-      <c r="AB44" s="9"/>
-      <c r="AC44" s="9"/>
-      <c r="AD44" s="9"/>
-      <c r="AE44" s="9"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="17"/>
+      <c r="Y44" s="17"/>
+      <c r="Z44" s="17"/>
+      <c r="AA44" s="17"/>
+      <c r="AB44" s="17"/>
+      <c r="AC44" s="17"/>
+      <c r="AD44" s="17"/>
+      <c r="AE44" s="17"/>
     </row>
     <row r="45" spans="3:31" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
-      <c r="V45" s="9"/>
-      <c r="W45" s="9"/>
-      <c r="X45" s="9"/>
-      <c r="Y45" s="9"/>
-      <c r="Z45" s="9"/>
-      <c r="AA45" s="9"/>
-      <c r="AB45" s="9"/>
-      <c r="AC45" s="9"/>
-      <c r="AD45" s="9"/>
-      <c r="AE45" s="9"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="17"/>
+      <c r="AA45" s="17"/>
+      <c r="AB45" s="17"/>
+      <c r="AC45" s="17"/>
+      <c r="AD45" s="17"/>
+      <c r="AE45" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E18:Q18"/>
-    <mergeCell ref="E19:Q19"/>
-    <mergeCell ref="E20:Q20"/>
-    <mergeCell ref="E21:Q21"/>
-    <mergeCell ref="E15:Q15"/>
-    <mergeCell ref="S12:AE12"/>
-    <mergeCell ref="S13:AE13"/>
-    <mergeCell ref="S14:AE14"/>
-    <mergeCell ref="E16:Q16"/>
-    <mergeCell ref="E17:Q17"/>
-    <mergeCell ref="E10:Q10"/>
-    <mergeCell ref="E11:Q11"/>
-    <mergeCell ref="E12:Q12"/>
-    <mergeCell ref="E13:Q13"/>
-    <mergeCell ref="E14:Q14"/>
+    <mergeCell ref="E22:Q22"/>
+    <mergeCell ref="C34:AE45"/>
+    <mergeCell ref="S24:AE24"/>
+    <mergeCell ref="S25:AE25"/>
+    <mergeCell ref="E24:Q24"/>
+    <mergeCell ref="E25:Q25"/>
+    <mergeCell ref="S22:AE22"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="G6:L6"/>
     <mergeCell ref="O6:R6"/>
@@ -2319,13 +2338,21 @@
     <mergeCell ref="S15:AE15"/>
     <mergeCell ref="S16:AE16"/>
     <mergeCell ref="E23:Q23"/>
-    <mergeCell ref="E22:Q22"/>
-    <mergeCell ref="C34:AE45"/>
-    <mergeCell ref="S24:AE24"/>
-    <mergeCell ref="S25:AE25"/>
-    <mergeCell ref="E24:Q24"/>
-    <mergeCell ref="E25:Q25"/>
-    <mergeCell ref="S22:AE22"/>
+    <mergeCell ref="E10:Q10"/>
+    <mergeCell ref="E11:Q11"/>
+    <mergeCell ref="E12:Q12"/>
+    <mergeCell ref="E13:Q13"/>
+    <mergeCell ref="E14:Q14"/>
+    <mergeCell ref="S12:AE12"/>
+    <mergeCell ref="S13:AE13"/>
+    <mergeCell ref="S14:AE14"/>
+    <mergeCell ref="E16:Q16"/>
+    <mergeCell ref="E17:Q17"/>
+    <mergeCell ref="E18:Q18"/>
+    <mergeCell ref="E19:Q19"/>
+    <mergeCell ref="E20:Q20"/>
+    <mergeCell ref="E21:Q21"/>
+    <mergeCell ref="E15:Q15"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
@@ -2342,6 +2369,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -2596,27 +2643,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A996CA-C060-4A23-AF4C-04B99D67DD5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615888F5-DC3B-4D8B-A082-1F479BBD3D8A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{585AE2C1-D657-45D2-B6FC-459B6B32B62D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2633,23 +2679,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615888F5-DC3B-4D8B-A082-1F479BBD3D8A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A996CA-C060-4A23-AF4C-04B99D67DD5D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/実装ノート.xlsx
+++ b/実装ノート.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3C20EF-951D-471F-B63D-D90A85874E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EDFA61-E22D-498C-B37B-3A7AF8690FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -504,7 +504,36 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">・ 敵に吹っ飛ばされた時の再スポーンの吹っ飛ばしを無効化
+    <t>マップデータの書き込み時の例外スロー対策(詳細は特質事項に記入)</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>トクシツジコウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの被ダメージ時、ダメージを受けた方向に向かせる + アニメーションを追加</t>
+    <rPh sb="6" eb="7">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ 敵に吹っ飛ばされた時の再スポーンの吹っ飛ばしを無効化
 ・ 再スポーン時にジャンプを無効化
 ・ 遠距離敵の攻撃タイミングを調整
 ・ プレイヤーが床下にいるとき、デーモンはアニメーションを待機状態にする
@@ -512,10 +541,9 @@
 ・ステージのブロック生成の生成する順番を"前→奥"から"奥→前"に変更
 　↳ これにより、データどうりの見た目で生成されるようになる
 ・ステージデータに「生成最大数を超えたデータを入力」したときに、最大数以上のデータは読み込まないようにする
-　↳ 例:) 生成最大数30×30でセル番号(BA,40)に生成しても正常に動作する
 ・ステージデータの読み込む領域で「未入力」か「データ数値外」か「文字列が含まれる」のとき、
-　"空のモデル"を描画して例外スローを対策
-・ </t>
+  "空のモデル"を代わりに生成
+・ ステージデータファイルが無い・ファイル名が違うとき、"空のブロックモデル"を代わりに生成</t>
     <rPh sb="2" eb="3">
       <t>テキ</t>
     </rPh>
@@ -570,126 +598,101 @@
     <rPh sb="130" eb="132">
       <t>コウゲキ</t>
     </rPh>
+    <rPh sb="155" eb="156">
+      <t>マエ</t>
+    </rPh>
     <rPh sb="157" eb="158">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="162" eb="163">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="164" eb="165">
       <t>マエ</t>
     </rPh>
-    <rPh sb="159" eb="160">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="164" eb="165">
-      <t>オク</t>
-    </rPh>
-    <rPh sb="166" eb="167">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="169" eb="171">
+    <rPh sb="167" eb="169">
       <t>ヘンコウ</t>
     </rPh>
+    <rPh sb="183" eb="184">
+      <t>ミ</t>
+    </rPh>
     <rPh sb="185" eb="186">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="187" eb="188">
       <t>メ</t>
     </rPh>
-    <rPh sb="189" eb="191">
+    <rPh sb="187" eb="189">
       <t>セイセイ</t>
     </rPh>
-    <rPh sb="209" eb="211">
+    <rPh sb="213" eb="214">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="220" eb="222">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="228" eb="230">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="232" eb="235">
+      <t>サイダイスウ</t>
+    </rPh>
+    <rPh sb="235" eb="237">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="242" eb="243">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="244" eb="245">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="262" eb="263">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="264" eb="266">
+      <t>リョウイキ</t>
+    </rPh>
+    <rPh sb="268" eb="271">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="277" eb="279">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="279" eb="280">
+      <t>ガイ</t>
+    </rPh>
+    <rPh sb="283" eb="286">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="287" eb="288">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="303" eb="304">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="307" eb="309">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="310" eb="311">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="314" eb="316">
       <t>セイセイ</t>
     </rPh>
-    <rPh sb="216" eb="217">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="223" eb="225">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="231" eb="233">
-      <t>レイガイ</t>
-    </rPh>
-    <rPh sb="235" eb="238">
-      <t>サイダイスウ</t>
-    </rPh>
-    <rPh sb="238" eb="240">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="245" eb="246">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="247" eb="248">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="257" eb="258">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="261" eb="265">
-      <t>セイセイサイダイ</t>
-    </rPh>
-    <rPh sb="265" eb="266">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="274" eb="276">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="284" eb="286">
+    <rPh sb="331" eb="332">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="338" eb="339">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="340" eb="341">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="346" eb="347">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="357" eb="358">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="361" eb="363">
       <t>セイセイ</t>
-    </rPh>
-    <rPh sb="289" eb="291">
-      <t>セイジョウ</t>
-    </rPh>
-    <rPh sb="292" eb="294">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="306" eb="307">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="308" eb="309">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="310" eb="312">
-      <t>リョウイキ</t>
-    </rPh>
-    <rPh sb="314" eb="317">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="323" eb="325">
-      <t>スウチ</t>
-    </rPh>
-    <rPh sb="325" eb="326">
-      <t>ガイ</t>
-    </rPh>
-    <rPh sb="329" eb="332">
-      <t>モジレツ</t>
-    </rPh>
-    <rPh sb="333" eb="334">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="345" eb="346">
-      <t>カラ</t>
-    </rPh>
-    <rPh sb="348" eb="349">
-      <t>カラ</t>
-    </rPh>
-    <rPh sb="352" eb="354">
-      <t>ビョウガ</t>
-    </rPh>
-    <rPh sb="356" eb="358">
-      <t>レイガイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マップデータの書き込み時の例外スロー対策(詳細は特質事項に記入)</t>
-    <rPh sb="7" eb="9">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="24" eb="28">
-      <t>トクシツジコウ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>キニュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1175,7 +1178,7 @@
     <col min="6" max="18" width="2.5" style="2"/>
     <col min="19" max="19" width="2.5" style="2" customWidth="1"/>
     <col min="20" max="30" width="2.5" style="2"/>
-    <col min="31" max="31" width="29.33203125" style="2" customWidth="1"/>
+    <col min="31" max="31" width="35.1640625" style="2" customWidth="1"/>
     <col min="32" max="16384" width="2.5" style="2"/>
   </cols>
   <sheetData>
@@ -1435,7 +1438,7 @@
         <v>50</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T14" s="10"/>
       <c r="U14" s="10"/>
@@ -1472,8 +1475,12 @@
       <c r="O15" s="10"/>
       <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="7"/>
+      <c r="R15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
@@ -1775,21 +1782,21 @@
       <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
       <c r="R23" s="6"/>
-      <c r="S23" s="10" t="s">
+      <c r="S23" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
-      <c r="V23" s="10"/>
-      <c r="W23" s="10"/>
-      <c r="X23" s="10"/>
-      <c r="Y23" s="10"/>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10"/>
-      <c r="AB23" s="10"/>
-      <c r="AC23" s="10"/>
-      <c r="AD23" s="10"/>
-      <c r="AE23" s="10"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="18"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="18"/>
+      <c r="Z23" s="18"/>
+      <c r="AA23" s="18"/>
+      <c r="AB23" s="18"/>
+      <c r="AC23" s="18"/>
+      <c r="AD23" s="18"/>
+      <c r="AE23" s="18"/>
     </row>
     <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="5" t="s">
@@ -1814,21 +1821,21 @@
       <c r="P24" s="10"/>
       <c r="Q24" s="10"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="10" t="s">
+      <c r="S24" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="T24" s="10"/>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10"/>
-      <c r="Y24" s="10"/>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10"/>
-      <c r="AB24" s="10"/>
-      <c r="AC24" s="10"/>
-      <c r="AD24" s="10"/>
-      <c r="AE24" s="10"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
+      <c r="W24" s="18"/>
+      <c r="X24" s="18"/>
+      <c r="Y24" s="18"/>
+      <c r="Z24" s="18"/>
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="18"/>
+      <c r="AD24" s="18"/>
+      <c r="AE24" s="18"/>
     </row>
     <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="5" t="s">
@@ -1853,21 +1860,21 @@
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="6"/>
-      <c r="S25" s="10" t="s">
+      <c r="S25" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10"/>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10"/>
-      <c r="AB25" s="10"/>
-      <c r="AC25" s="10"/>
-      <c r="AD25" s="10"/>
-      <c r="AE25" s="10"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="18"/>
+      <c r="V25" s="18"/>
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="18"/>
+      <c r="Z25" s="18"/>
+      <c r="AA25" s="18"/>
+      <c r="AB25" s="18"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="18"/>
+      <c r="AE25" s="18"/>
     </row>
     <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D27" s="3" t="s">
@@ -1941,7 +1948,7 @@
     </row>
     <row r="34" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C34" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>

--- a/実装ノート.xlsx
+++ b/実装ノート.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EDFA61-E22D-498C-B37B-3A7AF8690FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37049A3-0D33-4E5A-8A51-34615566188C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -693,6 +693,16 @@
     </rPh>
     <rPh sb="361" eb="363">
       <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FPS制御(TABキーでFPS表示)</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -852,20 +862,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -879,14 +886,17 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1188,36 +1198,36 @@
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13">
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="12">
         <v>2416026</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="O6" s="12" t="s">
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="O6" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="13" t="s">
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C7" s="3"/>
@@ -1255,39 +1265,39 @@
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
       <c r="R10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S10" s="15" t="s">
+      <c r="S10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="15"/>
-      <c r="Z10" s="15"/>
-      <c r="AA10" s="15"/>
-      <c r="AB10" s="15"/>
-      <c r="AC10" s="15"/>
-      <c r="AD10" s="15"/>
-      <c r="AE10" s="15"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="14"/>
     </row>
     <row r="11" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C11" s="5" t="s">
@@ -1296,39 +1306,39 @@
       <c r="D11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
       <c r="R11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S11" s="10" t="s">
+      <c r="S11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
-      <c r="AC11" s="10"/>
-      <c r="AD11" s="10"/>
-      <c r="AE11" s="10"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C12" s="5" t="s">
@@ -1337,39 +1347,39 @@
       <c r="D12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
       <c r="R12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S12" s="10" t="s">
+      <c r="S12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C13" s="5" t="s">
@@ -1378,39 +1388,39 @@
       <c r="D13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
       <c r="R13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S13" s="10" t="s">
+      <c r="S13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="10"/>
-      <c r="AC13" s="10"/>
-      <c r="AD13" s="10"/>
-      <c r="AE13" s="10"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C14" s="5" t="s">
@@ -1419,39 +1429,39 @@
       <c r="D14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
       <c r="R14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S14" s="10" t="s">
+      <c r="S14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-      <c r="AA14" s="10"/>
-      <c r="AB14" s="10"/>
-      <c r="AC14" s="10"/>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="10"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C15" s="5" t="s">
@@ -1460,39 +1470,39 @@
       <c r="D15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
       <c r="R15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="7" t="s">
+      <c r="S15" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="9"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="17"/>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C16" s="5" t="s">
@@ -1501,35 +1511,39 @@
       <c r="D16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
-      <c r="AB16" s="10"/>
-      <c r="AC16" s="10"/>
-      <c r="AD16" s="10"/>
-      <c r="AE16" s="10"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
     </row>
     <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="5" t="s">
@@ -1538,35 +1552,35 @@
       <c r="D17" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="9"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="17"/>
       <c r="R17" s="6"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="10"/>
-      <c r="AA17" s="10"/>
-      <c r="AB17" s="10"/>
-      <c r="AC17" s="10"/>
-      <c r="AD17" s="10"/>
-      <c r="AE17" s="10"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="7"/>
     </row>
     <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="5" t="s">
@@ -1575,35 +1589,35 @@
       <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="9"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="17"/>
       <c r="R18" s="6"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
-      <c r="AC18" s="10"/>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
     </row>
     <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="5" t="s">
@@ -1612,35 +1626,35 @@
       <c r="D19" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="9"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="17"/>
       <c r="R19" s="6"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="10"/>
-      <c r="AC19" s="10"/>
-      <c r="AD19" s="10"/>
-      <c r="AE19" s="10"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
     </row>
     <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="5" t="s">
@@ -1649,37 +1663,37 @@
       <c r="D20" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
       <c r="R20" s="6"/>
-      <c r="S20" s="18" t="s">
+      <c r="S20" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="18"/>
-      <c r="AA20" s="18"/>
-      <c r="AB20" s="18"/>
-      <c r="AC20" s="18"/>
-      <c r="AD20" s="18"/>
-      <c r="AE20" s="18"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="10"/>
     </row>
     <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="5" t="s">
@@ -1688,37 +1702,37 @@
       <c r="D21" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
       <c r="R21" s="6"/>
-      <c r="S21" s="18" t="s">
+      <c r="S21" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="18"/>
-      <c r="AC21" s="18"/>
-      <c r="AD21" s="18"/>
-      <c r="AE21" s="18"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+      <c r="AD21" s="10"/>
+      <c r="AE21" s="10"/>
     </row>
     <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="5" t="s">
@@ -1727,37 +1741,37 @@
       <c r="D22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
       <c r="R22" s="6"/>
-      <c r="S22" s="18" t="s">
+      <c r="S22" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="18"/>
-      <c r="AA22" s="18"/>
-      <c r="AB22" s="18"/>
-      <c r="AC22" s="18"/>
-      <c r="AD22" s="18"/>
-      <c r="AE22" s="18"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10"/>
+      <c r="AB22" s="10"/>
+      <c r="AC22" s="10"/>
+      <c r="AD22" s="10"/>
+      <c r="AE22" s="10"/>
     </row>
     <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="5" t="s">
@@ -1766,37 +1780,37 @@
       <c r="D23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
       <c r="R23" s="6"/>
-      <c r="S23" s="18" t="s">
+      <c r="S23" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="18"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="18"/>
-      <c r="AA23" s="18"/>
-      <c r="AB23" s="18"/>
-      <c r="AC23" s="18"/>
-      <c r="AD23" s="18"/>
-      <c r="AE23" s="18"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10"/>
+      <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10"/>
     </row>
     <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="5" t="s">
@@ -1805,37 +1819,37 @@
       <c r="D24" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="18" t="s">
+      <c r="S24" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="18"/>
-      <c r="AB24" s="18"/>
-      <c r="AC24" s="18"/>
-      <c r="AD24" s="18"/>
-      <c r="AE24" s="18"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
+      <c r="AA24" s="10"/>
+      <c r="AB24" s="10"/>
+      <c r="AC24" s="10"/>
+      <c r="AD24" s="10"/>
+      <c r="AE24" s="10"/>
     </row>
     <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="5" t="s">
@@ -1844,37 +1858,37 @@
       <c r="D25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
       <c r="R25" s="6"/>
-      <c r="S25" s="18" t="s">
+      <c r="S25" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="T25" s="18"/>
-      <c r="U25" s="18"/>
-      <c r="V25" s="18"/>
-      <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="18"/>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="18"/>
-      <c r="AD25" s="18"/>
-      <c r="AE25" s="18"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
+      <c r="AA25" s="10"/>
+      <c r="AB25" s="10"/>
+      <c r="AC25" s="10"/>
+      <c r="AD25" s="10"/>
+      <c r="AE25" s="10"/>
     </row>
     <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D27" s="3" t="s">
@@ -1914,421 +1928,429 @@
       </c>
     </row>
     <row r="33" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="14"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
-      <c r="AD33" s="14"/>
-      <c r="AE33" s="14"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="13"/>
+      <c r="AC33" s="13"/>
+      <c r="AD33" s="13"/>
+      <c r="AE33" s="13"/>
     </row>
     <row r="34" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
-      <c r="Z34" s="17"/>
-      <c r="AA34" s="17"/>
-      <c r="AB34" s="17"/>
-      <c r="AC34" s="17"/>
-      <c r="AD34" s="17"/>
-      <c r="AE34" s="17"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="9"/>
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="9"/>
+      <c r="AC34" s="9"/>
+      <c r="AD34" s="9"/>
+      <c r="AE34" s="9"/>
     </row>
     <row r="35" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
-      <c r="Z35" s="17"/>
-      <c r="AA35" s="17"/>
-      <c r="AB35" s="17"/>
-      <c r="AC35" s="17"/>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="17"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="9"/>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
+      <c r="AD35" s="9"/>
+      <c r="AE35" s="9"/>
     </row>
     <row r="36" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
-      <c r="U36" s="17"/>
-      <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
-      <c r="X36" s="17"/>
-      <c r="Y36" s="17"/>
-      <c r="Z36" s="17"/>
-      <c r="AA36" s="17"/>
-      <c r="AB36" s="17"/>
-      <c r="AC36" s="17"/>
-      <c r="AD36" s="17"/>
-      <c r="AE36" s="17"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
+      <c r="AE36" s="9"/>
     </row>
     <row r="37" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17"/>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
-      <c r="X37" s="17"/>
-      <c r="Y37" s="17"/>
-      <c r="Z37" s="17"/>
-      <c r="AA37" s="17"/>
-      <c r="AB37" s="17"/>
-      <c r="AC37" s="17"/>
-      <c r="AD37" s="17"/>
-      <c r="AE37" s="17"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
+      <c r="AD37" s="9"/>
+      <c r="AE37" s="9"/>
     </row>
     <row r="38" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
-      <c r="X38" s="17"/>
-      <c r="Y38" s="17"/>
-      <c r="Z38" s="17"/>
-      <c r="AA38" s="17"/>
-      <c r="AB38" s="17"/>
-      <c r="AC38" s="17"/>
-      <c r="AD38" s="17"/>
-      <c r="AE38" s="17"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
+      <c r="AD38" s="9"/>
+      <c r="AE38" s="9"/>
     </row>
     <row r="39" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="17"/>
-      <c r="U39" s="17"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
-      <c r="X39" s="17"/>
-      <c r="Y39" s="17"/>
-      <c r="Z39" s="17"/>
-      <c r="AA39" s="17"/>
-      <c r="AB39" s="17"/>
-      <c r="AC39" s="17"/>
-      <c r="AD39" s="17"/>
-      <c r="AE39" s="17"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
+      <c r="AD39" s="9"/>
+      <c r="AE39" s="9"/>
     </row>
     <row r="40" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17"/>
-      <c r="O40" s="17"/>
-      <c r="P40" s="17"/>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-      <c r="T40" s="17"/>
-      <c r="U40" s="17"/>
-      <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
-      <c r="X40" s="17"/>
-      <c r="Y40" s="17"/>
-      <c r="Z40" s="17"/>
-      <c r="AA40" s="17"/>
-      <c r="AB40" s="17"/>
-      <c r="AC40" s="17"/>
-      <c r="AD40" s="17"/>
-      <c r="AE40" s="17"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="9"/>
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
+      <c r="AD40" s="9"/>
+      <c r="AE40" s="9"/>
     </row>
     <row r="41" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
-      <c r="X41" s="17"/>
-      <c r="Y41" s="17"/>
-      <c r="Z41" s="17"/>
-      <c r="AA41" s="17"/>
-      <c r="AB41" s="17"/>
-      <c r="AC41" s="17"/>
-      <c r="AD41" s="17"/>
-      <c r="AE41" s="17"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="9"/>
+      <c r="AA41" s="9"/>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="9"/>
+      <c r="AD41" s="9"/>
+      <c r="AE41" s="9"/>
     </row>
     <row r="42" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="17"/>
-      <c r="Y42" s="17"/>
-      <c r="Z42" s="17"/>
-      <c r="AA42" s="17"/>
-      <c r="AB42" s="17"/>
-      <c r="AC42" s="17"/>
-      <c r="AD42" s="17"/>
-      <c r="AE42" s="17"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9"/>
+      <c r="Y42" s="9"/>
+      <c r="Z42" s="9"/>
+      <c r="AA42" s="9"/>
+      <c r="AB42" s="9"/>
+      <c r="AC42" s="9"/>
+      <c r="AD42" s="9"/>
+      <c r="AE42" s="9"/>
     </row>
     <row r="43" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
-      <c r="T43" s="17"/>
-      <c r="U43" s="17"/>
-      <c r="V43" s="17"/>
-      <c r="W43" s="17"/>
-      <c r="X43" s="17"/>
-      <c r="Y43" s="17"/>
-      <c r="Z43" s="17"/>
-      <c r="AA43" s="17"/>
-      <c r="AB43" s="17"/>
-      <c r="AC43" s="17"/>
-      <c r="AD43" s="17"/>
-      <c r="AE43" s="17"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="9"/>
+      <c r="AA43" s="9"/>
+      <c r="AB43" s="9"/>
+      <c r="AC43" s="9"/>
+      <c r="AD43" s="9"/>
+      <c r="AE43" s="9"/>
     </row>
     <row r="44" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17"/>
-      <c r="U44" s="17"/>
-      <c r="V44" s="17"/>
-      <c r="W44" s="17"/>
-      <c r="X44" s="17"/>
-      <c r="Y44" s="17"/>
-      <c r="Z44" s="17"/>
-      <c r="AA44" s="17"/>
-      <c r="AB44" s="17"/>
-      <c r="AC44" s="17"/>
-      <c r="AD44" s="17"/>
-      <c r="AE44" s="17"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9"/>
+      <c r="R44" s="9"/>
+      <c r="S44" s="9"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="9"/>
+      <c r="AA44" s="9"/>
+      <c r="AB44" s="9"/>
+      <c r="AC44" s="9"/>
+      <c r="AD44" s="9"/>
+      <c r="AE44" s="9"/>
     </row>
     <row r="45" spans="3:31" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
-      <c r="Q45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
-      <c r="U45" s="17"/>
-      <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="17"/>
-      <c r="Y45" s="17"/>
-      <c r="Z45" s="17"/>
-      <c r="AA45" s="17"/>
-      <c r="AB45" s="17"/>
-      <c r="AC45" s="17"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="17"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="9"/>
+      <c r="Z45" s="9"/>
+      <c r="AA45" s="9"/>
+      <c r="AB45" s="9"/>
+      <c r="AC45" s="9"/>
+      <c r="AD45" s="9"/>
+      <c r="AE45" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E22:Q22"/>
-    <mergeCell ref="C34:AE45"/>
-    <mergeCell ref="S24:AE24"/>
-    <mergeCell ref="S25:AE25"/>
-    <mergeCell ref="E24:Q24"/>
-    <mergeCell ref="E25:Q25"/>
-    <mergeCell ref="S22:AE22"/>
+    <mergeCell ref="E18:Q18"/>
+    <mergeCell ref="E19:Q19"/>
+    <mergeCell ref="E20:Q20"/>
+    <mergeCell ref="E21:Q21"/>
+    <mergeCell ref="E15:Q15"/>
+    <mergeCell ref="S12:AE12"/>
+    <mergeCell ref="S13:AE13"/>
+    <mergeCell ref="S14:AE14"/>
+    <mergeCell ref="E16:Q16"/>
+    <mergeCell ref="E17:Q17"/>
+    <mergeCell ref="E10:Q10"/>
+    <mergeCell ref="E11:Q11"/>
+    <mergeCell ref="E12:Q12"/>
+    <mergeCell ref="E13:Q13"/>
+    <mergeCell ref="E14:Q14"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="G6:L6"/>
     <mergeCell ref="O6:R6"/>
@@ -2345,21 +2367,13 @@
     <mergeCell ref="S15:AE15"/>
     <mergeCell ref="S16:AE16"/>
     <mergeCell ref="E23:Q23"/>
-    <mergeCell ref="E10:Q10"/>
-    <mergeCell ref="E11:Q11"/>
-    <mergeCell ref="E12:Q12"/>
-    <mergeCell ref="E13:Q13"/>
-    <mergeCell ref="E14:Q14"/>
-    <mergeCell ref="S12:AE12"/>
-    <mergeCell ref="S13:AE13"/>
-    <mergeCell ref="S14:AE14"/>
-    <mergeCell ref="E16:Q16"/>
-    <mergeCell ref="E17:Q17"/>
-    <mergeCell ref="E18:Q18"/>
-    <mergeCell ref="E19:Q19"/>
-    <mergeCell ref="E20:Q20"/>
-    <mergeCell ref="E21:Q21"/>
-    <mergeCell ref="E15:Q15"/>
+    <mergeCell ref="E22:Q22"/>
+    <mergeCell ref="C34:AE45"/>
+    <mergeCell ref="S24:AE24"/>
+    <mergeCell ref="S25:AE25"/>
+    <mergeCell ref="E24:Q24"/>
+    <mergeCell ref="E25:Q25"/>
+    <mergeCell ref="S22:AE22"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
@@ -2376,26 +2390,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -2650,26 +2644,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A996CA-C060-4A23-AF4C-04B99D67DD5D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615888F5-DC3B-4D8B-A082-1F479BBD3D8A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{585AE2C1-D657-45D2-B6FC-459B6B32B62D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2686,4 +2681,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615888F5-DC3B-4D8B-A082-1F479BBD3D8A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A996CA-C060-4A23-AF4C-04B99D67DD5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/実装ノート.xlsx
+++ b/実装ノート.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37049A3-0D33-4E5A-8A51-34615566188C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36069ED3-2EA8-44E1-8695-8C6012D35CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="58">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -392,75 +392,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>エネミー３種以上</t>
-    <rPh sb="5" eb="6">
-      <t>シュ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エネミー３種以上で、異なる攻撃</t>
-    <rPh sb="5" eb="6">
-      <t>シュ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>コト</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤー武器３種以上</t>
-    <rPh sb="5" eb="7">
-      <t>ブキ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>シュ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>イジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エネミー３種以上で、異なる移動</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３次元マップ(壁がある)</t>
-    <rPh sb="1" eb="3">
-      <t>ジゲン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>カベ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>３次元マップ(壁)とプレイヤーの衝突判定</t>
-    <rPh sb="1" eb="3">
-      <t>ジゲン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>カベ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ショウトツ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>✅</t>
   </si>
   <si>
@@ -533,11 +464,61 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>FPS制御(TABキーでFPS表示)</t>
+    <rPh sb="3" eb="5">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３次元マップ(壁)とプレイヤーの衝突判定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>３次元マップ(壁がある)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー武器３種以上</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規エネミー：ジャイアント追加</t>
+    <rPh sb="0" eb="2">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>跳ねる敵の弾追加</t>
+    <rPh sb="0" eb="1">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>・ 敵に吹っ飛ばされた時の再スポーンの吹っ飛ばしを無効化
 ・ 再スポーン時にジャンプを無効化
 ・ 遠距離敵の攻撃タイミングを調整
+・ プレイヤー落下時も、攻撃を無効化
 ・ プレイヤーが床下にいるとき、デーモンはアニメーションを待機状態にする
 ・ プレイヤーが床下にいるとき、遠距離の弾がプレイヤーに攻撃する
+・ ウィザードとデーモンをすべて倒すと、ジャイアントが召喚され、倒すとゲームクリア
 ・ステージのブロック生成の生成する順番を"前→奥"から"奥→前"に変更
 　↳ これにより、データどうりの見た目で生成されるようになる
 ・ステージデータに「生成最大数を超えたデータを入力」したときに、最大数以上のデータは読み込まないようにする
@@ -580,129 +561,128 @@
     <rPh sb="62" eb="64">
       <t>チョウセイ</t>
     </rPh>
-    <rPh sb="73" eb="74">
+    <rPh sb="92" eb="93">
       <t>ユカ</t>
     </rPh>
-    <rPh sb="74" eb="75">
+    <rPh sb="93" eb="94">
       <t>シタ</t>
     </rPh>
-    <rPh sb="111" eb="112">
+    <rPh sb="130" eb="131">
       <t>シタ</t>
     </rPh>
-    <rPh sb="118" eb="121">
+    <rPh sb="137" eb="140">
       <t>エンキョリ</t>
     </rPh>
-    <rPh sb="122" eb="123">
+    <rPh sb="141" eb="142">
       <t>タマ</t>
     </rPh>
-    <rPh sb="130" eb="132">
+    <rPh sb="149" eb="151">
       <t>コウゲキ</t>
     </rPh>
-    <rPh sb="155" eb="156">
+    <rPh sb="171" eb="172">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="182" eb="184">
+      <t>ショウカン</t>
+    </rPh>
+    <rPh sb="187" eb="188">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="217" eb="218">
       <t>マエ</t>
     </rPh>
-    <rPh sb="157" eb="158">
+    <rPh sb="219" eb="220">
       <t>オク</t>
     </rPh>
-    <rPh sb="162" eb="163">
+    <rPh sb="224" eb="225">
       <t>オク</t>
     </rPh>
-    <rPh sb="164" eb="165">
+    <rPh sb="226" eb="227">
       <t>マエ</t>
     </rPh>
-    <rPh sb="167" eb="169">
+    <rPh sb="229" eb="231">
       <t>ヘンコウ</t>
     </rPh>
-    <rPh sb="183" eb="184">
+    <rPh sb="245" eb="246">
       <t>ミ</t>
     </rPh>
-    <rPh sb="185" eb="186">
+    <rPh sb="247" eb="248">
       <t>メ</t>
     </rPh>
-    <rPh sb="187" eb="189">
+    <rPh sb="249" eb="251">
       <t>セイセイ</t>
     </rPh>
-    <rPh sb="213" eb="214">
+    <rPh sb="275" eb="276">
       <t>コ</t>
     </rPh>
-    <rPh sb="220" eb="222">
+    <rPh sb="282" eb="284">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="228" eb="230">
+    <rPh sb="290" eb="292">
       <t>レイガイ</t>
     </rPh>
-    <rPh sb="232" eb="235">
+    <rPh sb="294" eb="297">
       <t>サイダイスウ</t>
     </rPh>
-    <rPh sb="235" eb="237">
+    <rPh sb="297" eb="299">
       <t>イジョウ</t>
     </rPh>
-    <rPh sb="242" eb="243">
+    <rPh sb="304" eb="305">
       <t>ヨ</t>
     </rPh>
-    <rPh sb="244" eb="245">
+    <rPh sb="306" eb="307">
       <t>コ</t>
     </rPh>
-    <rPh sb="262" eb="263">
+    <rPh sb="324" eb="325">
       <t>コ</t>
     </rPh>
-    <rPh sb="264" eb="266">
+    <rPh sb="326" eb="328">
       <t>リョウイキ</t>
     </rPh>
-    <rPh sb="268" eb="271">
+    <rPh sb="330" eb="333">
       <t>ミニュウリョク</t>
     </rPh>
-    <rPh sb="277" eb="279">
+    <rPh sb="339" eb="341">
       <t>スウチ</t>
     </rPh>
-    <rPh sb="279" eb="280">
+    <rPh sb="341" eb="342">
       <t>ガイ</t>
     </rPh>
-    <rPh sb="283" eb="286">
+    <rPh sb="345" eb="348">
       <t>モジレツ</t>
     </rPh>
-    <rPh sb="287" eb="288">
+    <rPh sb="349" eb="350">
       <t>フク</t>
     </rPh>
-    <rPh sb="303" eb="304">
+    <rPh sb="365" eb="366">
       <t>カラ</t>
     </rPh>
-    <rPh sb="307" eb="309">
+    <rPh sb="369" eb="371">
       <t>ビョウガ</t>
     </rPh>
-    <rPh sb="310" eb="311">
+    <rPh sb="372" eb="373">
       <t>カ</t>
     </rPh>
-    <rPh sb="314" eb="316">
+    <rPh sb="376" eb="378">
       <t>セイセイ</t>
     </rPh>
-    <rPh sb="331" eb="332">
+    <rPh sb="393" eb="394">
       <t>ナ</t>
     </rPh>
-    <rPh sb="338" eb="339">
+    <rPh sb="400" eb="401">
       <t>メイ</t>
     </rPh>
-    <rPh sb="340" eb="341">
+    <rPh sb="402" eb="403">
       <t>チガ</t>
     </rPh>
-    <rPh sb="346" eb="347">
+    <rPh sb="408" eb="409">
       <t>カラ</t>
     </rPh>
-    <rPh sb="357" eb="358">
+    <rPh sb="419" eb="420">
       <t>カ</t>
     </rPh>
-    <rPh sb="361" eb="363">
+    <rPh sb="423" eb="425">
       <t>セイセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>FPS制御(TABキーでFPS表示)</t>
-    <rPh sb="3" eb="5">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -862,17 +842,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -883,20 +866,17 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1198,36 +1178,36 @@
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12">
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13">
         <v>2416026</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="O6" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
-      <c r="S6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="O6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C7" s="3"/>
@@ -1265,423 +1245,429 @@
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
       <c r="R10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S10" s="14" t="s">
+      <c r="S10" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
-      <c r="AD10" s="14"/>
-      <c r="AE10" s="14"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
     </row>
     <row r="11" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C11" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
       <c r="R11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
-      <c r="AE11" s="7"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="10"/>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
       <c r="R12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
-      <c r="AE12" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C13" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
       <c r="R13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
-      <c r="AE13" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="S13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="10"/>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C14" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
       <c r="R14" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
-      <c r="AE14" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="S14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S15" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="16"/>
-      <c r="AE15" s="17"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="8"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="8"/>
+      <c r="AC15" s="8"/>
+      <c r="AD15" s="8"/>
+      <c r="AE15" s="9"/>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
       <c r="R16" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
-      <c r="AE16" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="S16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
     </row>
     <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
-      <c r="AE17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
+      <c r="AB17" s="10"/>
+      <c r="AC17" s="10"/>
+      <c r="AD17" s="10"/>
+      <c r="AE17" s="10"/>
     </row>
     <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7"/>
-      <c r="AE18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
     </row>
     <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="17"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="9"/>
       <c r="R19" s="6"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7"/>
-      <c r="AE19" s="7"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+      <c r="AD19" s="10"/>
+      <c r="AE19" s="10"/>
     </row>
     <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
       <c r="R20" s="6"/>
-      <c r="S20" s="10" t="s">
-        <v>46</v>
-      </c>
+      <c r="S20" s="10"/>
       <c r="T20" s="10"/>
       <c r="U20" s="10"/>
       <c r="V20" s="10"/>
@@ -1700,66 +1686,62 @@
         <v>13</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
       <c r="R21" s="6"/>
-      <c r="S21" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
-      <c r="Y21" s="10"/>
-      <c r="Z21" s="10"/>
-      <c r="AA21" s="10"/>
-      <c r="AB21" s="10"/>
-      <c r="AC21" s="10"/>
-      <c r="AD21" s="10"/>
-      <c r="AE21" s="10"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="15"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
+      <c r="AA21" s="15"/>
+      <c r="AB21" s="15"/>
+      <c r="AC21" s="15"/>
+      <c r="AD21" s="15"/>
+      <c r="AE21" s="15"/>
     </row>
     <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
       <c r="R22" s="6"/>
-      <c r="S22" s="10" t="s">
-        <v>49</v>
-      </c>
+      <c r="S22" s="10"/>
       <c r="T22" s="10"/>
       <c r="U22" s="10"/>
       <c r="V22" s="10"/>
@@ -1778,117 +1760,117 @@
         <v>14</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
       <c r="R23" s="6"/>
-      <c r="S23" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
-      <c r="V23" s="10"/>
-      <c r="W23" s="10"/>
-      <c r="X23" s="10"/>
-      <c r="Y23" s="10"/>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10"/>
-      <c r="AB23" s="10"/>
-      <c r="AC23" s="10"/>
-      <c r="AD23" s="10"/>
-      <c r="AE23" s="10"/>
+      <c r="S23" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15"/>
+      <c r="AB23" s="15"/>
+      <c r="AC23" s="15"/>
+      <c r="AD23" s="15"/>
+      <c r="AE23" s="15"/>
     </row>
     <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="T24" s="10"/>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10"/>
-      <c r="Y24" s="10"/>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10"/>
-      <c r="AB24" s="10"/>
-      <c r="AC24" s="10"/>
-      <c r="AD24" s="10"/>
-      <c r="AE24" s="10"/>
+      <c r="S24" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
     </row>
     <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
       <c r="R25" s="6"/>
-      <c r="S25" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10"/>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10"/>
-      <c r="AB25" s="10"/>
-      <c r="AC25" s="10"/>
-      <c r="AD25" s="10"/>
-      <c r="AE25" s="10"/>
+      <c r="S25" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="T25" s="15"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15"/>
+      <c r="Z25" s="15"/>
+      <c r="AA25" s="15"/>
+      <c r="AB25" s="15"/>
+      <c r="AC25" s="15"/>
+      <c r="AD25" s="15"/>
+      <c r="AE25" s="15"/>
     </row>
     <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="D27" s="3" t="s">
@@ -1928,429 +1910,421 @@
       </c>
     </row>
     <row r="33" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="13"/>
-      <c r="S33" s="13"/>
-      <c r="T33" s="13"/>
-      <c r="U33" s="13"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="13"/>
-      <c r="X33" s="13"/>
-      <c r="Y33" s="13"/>
-      <c r="Z33" s="13"/>
-      <c r="AA33" s="13"/>
-      <c r="AB33" s="13"/>
-      <c r="AC33" s="13"/>
-      <c r="AD33" s="13"/>
-      <c r="AE33" s="13"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
     </row>
     <row r="34" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="9"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="9"/>
-      <c r="AE34" s="9"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="18"/>
+      <c r="X34" s="18"/>
+      <c r="Y34" s="18"/>
+      <c r="Z34" s="18"/>
+      <c r="AA34" s="18"/>
+      <c r="AB34" s="18"/>
+      <c r="AC34" s="18"/>
+      <c r="AD34" s="18"/>
+      <c r="AE34" s="18"/>
     </row>
     <row r="35" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9"/>
-      <c r="Y35" s="9"/>
-      <c r="Z35" s="9"/>
-      <c r="AA35" s="9"/>
-      <c r="AB35" s="9"/>
-      <c r="AC35" s="9"/>
-      <c r="AD35" s="9"/>
-      <c r="AE35" s="9"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="18"/>
+      <c r="Z35" s="18"/>
+      <c r="AA35" s="18"/>
+      <c r="AB35" s="18"/>
+      <c r="AC35" s="18"/>
+      <c r="AD35" s="18"/>
+      <c r="AE35" s="18"/>
     </row>
     <row r="36" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="9"/>
-      <c r="AE36" s="9"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="18"/>
+      <c r="X36" s="18"/>
+      <c r="Y36" s="18"/>
+      <c r="Z36" s="18"/>
+      <c r="AA36" s="18"/>
+      <c r="AB36" s="18"/>
+      <c r="AC36" s="18"/>
+      <c r="AD36" s="18"/>
+      <c r="AE36" s="18"/>
     </row>
     <row r="37" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="9"/>
-      <c r="X37" s="9"/>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="9"/>
-      <c r="AA37" s="9"/>
-      <c r="AB37" s="9"/>
-      <c r="AC37" s="9"/>
-      <c r="AD37" s="9"/>
-      <c r="AE37" s="9"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="18"/>
+      <c r="Z37" s="18"/>
+      <c r="AA37" s="18"/>
+      <c r="AB37" s="18"/>
+      <c r="AC37" s="18"/>
+      <c r="AD37" s="18"/>
+      <c r="AE37" s="18"/>
     </row>
     <row r="38" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="9"/>
-      <c r="X38" s="9"/>
-      <c r="Y38" s="9"/>
-      <c r="Z38" s="9"/>
-      <c r="AA38" s="9"/>
-      <c r="AB38" s="9"/>
-      <c r="AC38" s="9"/>
-      <c r="AD38" s="9"/>
-      <c r="AE38" s="9"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
+      <c r="Z38" s="18"/>
+      <c r="AA38" s="18"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="18"/>
+      <c r="AE38" s="18"/>
     </row>
     <row r="39" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="9"/>
-      <c r="AE39" s="9"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="18"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
+      <c r="Z39" s="18"/>
+      <c r="AA39" s="18"/>
+      <c r="AB39" s="18"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="18"/>
+      <c r="AE39" s="18"/>
     </row>
     <row r="40" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="R40" s="9"/>
-      <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
-      <c r="U40" s="9"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="9"/>
-      <c r="X40" s="9"/>
-      <c r="Y40" s="9"/>
-      <c r="Z40" s="9"/>
-      <c r="AA40" s="9"/>
-      <c r="AB40" s="9"/>
-      <c r="AC40" s="9"/>
-      <c r="AD40" s="9"/>
-      <c r="AE40" s="9"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="18"/>
+      <c r="Z40" s="18"/>
+      <c r="AA40" s="18"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="18"/>
+      <c r="AE40" s="18"/>
     </row>
     <row r="41" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="9"/>
-      <c r="X41" s="9"/>
-      <c r="Y41" s="9"/>
-      <c r="Z41" s="9"/>
-      <c r="AA41" s="9"/>
-      <c r="AB41" s="9"/>
-      <c r="AC41" s="9"/>
-      <c r="AD41" s="9"/>
-      <c r="AE41" s="9"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="18"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="18"/>
+      <c r="Z41" s="18"/>
+      <c r="AA41" s="18"/>
+      <c r="AB41" s="18"/>
+      <c r="AC41" s="18"/>
+      <c r="AD41" s="18"/>
+      <c r="AE41" s="18"/>
     </row>
     <row r="42" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="R42" s="9"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="9"/>
-      <c r="AE42" s="9"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="18"/>
+      <c r="R42" s="18"/>
+      <c r="S42" s="18"/>
+      <c r="T42" s="18"/>
+      <c r="U42" s="18"/>
+      <c r="V42" s="18"/>
+      <c r="W42" s="18"/>
+      <c r="X42" s="18"/>
+      <c r="Y42" s="18"/>
+      <c r="Z42" s="18"/>
+      <c r="AA42" s="18"/>
+      <c r="AB42" s="18"/>
+      <c r="AC42" s="18"/>
+      <c r="AD42" s="18"/>
+      <c r="AE42" s="18"/>
     </row>
     <row r="43" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="9"/>
-      <c r="AE43" s="9"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="18"/>
+      <c r="AA43" s="18"/>
+      <c r="AB43" s="18"/>
+      <c r="AC43" s="18"/>
+      <c r="AD43" s="18"/>
+      <c r="AE43" s="18"/>
     </row>
     <row r="44" spans="3:31" x14ac:dyDescent="0.2">
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9"/>
-      <c r="R44" s="9"/>
-      <c r="S44" s="9"/>
-      <c r="T44" s="9"/>
-      <c r="U44" s="9"/>
-      <c r="V44" s="9"/>
-      <c r="W44" s="9"/>
-      <c r="X44" s="9"/>
-      <c r="Y44" s="9"/>
-      <c r="Z44" s="9"/>
-      <c r="AA44" s="9"/>
-      <c r="AB44" s="9"/>
-      <c r="AC44" s="9"/>
-      <c r="AD44" s="9"/>
-      <c r="AE44" s="9"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="18"/>
+      <c r="X44" s="18"/>
+      <c r="Y44" s="18"/>
+      <c r="Z44" s="18"/>
+      <c r="AA44" s="18"/>
+      <c r="AB44" s="18"/>
+      <c r="AC44" s="18"/>
+      <c r="AD44" s="18"/>
+      <c r="AE44" s="18"/>
     </row>
     <row r="45" spans="3:31" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
-      <c r="V45" s="9"/>
-      <c r="W45" s="9"/>
-      <c r="X45" s="9"/>
-      <c r="Y45" s="9"/>
-      <c r="Z45" s="9"/>
-      <c r="AA45" s="9"/>
-      <c r="AB45" s="9"/>
-      <c r="AC45" s="9"/>
-      <c r="AD45" s="9"/>
-      <c r="AE45" s="9"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="18"/>
+      <c r="AB45" s="18"/>
+      <c r="AC45" s="18"/>
+      <c r="AD45" s="18"/>
+      <c r="AE45" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="E18:Q18"/>
-    <mergeCell ref="E19:Q19"/>
-    <mergeCell ref="E20:Q20"/>
-    <mergeCell ref="E21:Q21"/>
-    <mergeCell ref="E15:Q15"/>
-    <mergeCell ref="S12:AE12"/>
-    <mergeCell ref="S13:AE13"/>
-    <mergeCell ref="S14:AE14"/>
-    <mergeCell ref="E16:Q16"/>
-    <mergeCell ref="E17:Q17"/>
-    <mergeCell ref="E10:Q10"/>
-    <mergeCell ref="E11:Q11"/>
-    <mergeCell ref="E12:Q12"/>
-    <mergeCell ref="E13:Q13"/>
-    <mergeCell ref="E14:Q14"/>
+    <mergeCell ref="E22:Q22"/>
+    <mergeCell ref="C34:AE45"/>
+    <mergeCell ref="S24:AE24"/>
+    <mergeCell ref="S25:AE25"/>
+    <mergeCell ref="E24:Q24"/>
+    <mergeCell ref="E25:Q25"/>
+    <mergeCell ref="S22:AE22"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="G6:L6"/>
     <mergeCell ref="O6:R6"/>
@@ -2367,13 +2341,21 @@
     <mergeCell ref="S15:AE15"/>
     <mergeCell ref="S16:AE16"/>
     <mergeCell ref="E23:Q23"/>
-    <mergeCell ref="E22:Q22"/>
-    <mergeCell ref="C34:AE45"/>
-    <mergeCell ref="S24:AE24"/>
-    <mergeCell ref="S25:AE25"/>
-    <mergeCell ref="E24:Q24"/>
-    <mergeCell ref="E25:Q25"/>
-    <mergeCell ref="S22:AE22"/>
+    <mergeCell ref="E10:Q10"/>
+    <mergeCell ref="E11:Q11"/>
+    <mergeCell ref="E12:Q12"/>
+    <mergeCell ref="E13:Q13"/>
+    <mergeCell ref="E14:Q14"/>
+    <mergeCell ref="S12:AE12"/>
+    <mergeCell ref="S13:AE13"/>
+    <mergeCell ref="S14:AE14"/>
+    <mergeCell ref="E16:Q16"/>
+    <mergeCell ref="E17:Q17"/>
+    <mergeCell ref="E18:Q18"/>
+    <mergeCell ref="E19:Q19"/>
+    <mergeCell ref="E20:Q20"/>
+    <mergeCell ref="E21:Q21"/>
+    <mergeCell ref="E15:Q15"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
@@ -2390,6 +2372,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -2644,27 +2646,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A996CA-C060-4A23-AF4C-04B99D67DD5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615888F5-DC3B-4D8B-A082-1F479BBD3D8A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{585AE2C1-D657-45D2-B6FC-459B6B32B62D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2681,23 +2682,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{615888F5-DC3B-4D8B-A082-1F479BBD3D8A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A996CA-C060-4A23-AF4C-04B99D67DD5D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>